--- a/downloadfile/문제자료/question_upload_template(test1).xlsx
+++ b/downloadfile/문제자료/question_upload_template(test1).xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/project/create_quiz_ai/downloadfile/문제자료/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F3BD5D7-FE33-C24D-93BA-BCAFE4EE17D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151337EF-1E75-4D45-9DB5-9B67A1E2A121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45760" yWindow="1260" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75400" yWindow="-1460" windowWidth="47880" windowHeight="31740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문제입력" sheetId="1" r:id="rId1"/>
     <sheet name="문제유형목록" sheetId="2" r:id="rId2"/>
+    <sheet name="출처" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="240">
   <si>
     <t>문제유형</t>
   </si>
@@ -609,13 +610,151 @@
   </si>
   <si>
     <t>AI는 독창성(originality)과 진정한 고유성(genuine uniqueness)을 제한할 위험이 있다.</t>
+  </si>
+  <si>
+    <t>출처1</t>
+  </si>
+  <si>
+    <t>출처1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출처2</t>
+  </si>
+  <si>
+    <t>출처2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출처3</t>
+  </si>
+  <si>
+    <t>출처3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통영어1</t>
+  </si>
+  <si>
+    <t>출처종류</t>
+  </si>
+  <si>
+    <t>출처종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교과서</t>
+  </si>
+  <si>
+    <t>모의고사</t>
+  </si>
+  <si>
+    <t>모의고사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출처4</t>
+  </si>
+  <si>
+    <t>출처4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25년</t>
+  </si>
+  <si>
+    <t>고2</t>
+  </si>
+  <si>
+    <t>10월</t>
+  </si>
+  <si>
+    <t>NE능률</t>
+  </si>
+  <si>
+    <t>민병천</t>
+  </si>
+  <si>
+    <t>오선영</t>
+  </si>
+  <si>
+    <t>YBM</t>
+  </si>
+  <si>
+    <t>박준언</t>
+  </si>
+  <si>
+    <t>김은형</t>
+  </si>
+  <si>
+    <t>동아</t>
+  </si>
+  <si>
+    <t>이병민</t>
+  </si>
+  <si>
+    <t>천재</t>
+  </si>
+  <si>
+    <t>강상구</t>
+  </si>
+  <si>
+    <t>조수경</t>
+  </si>
+  <si>
+    <t>비상</t>
+  </si>
+  <si>
+    <t>홍민표</t>
+  </si>
+  <si>
+    <t>미래엔</t>
+  </si>
+  <si>
+    <t>다락원</t>
+  </si>
+  <si>
+    <t>김길중</t>
+  </si>
+  <si>
+    <t>지학사</t>
+  </si>
+  <si>
+    <t>신상근</t>
+  </si>
+  <si>
+    <t>금성</t>
+  </si>
+  <si>
+    <t>최인철</t>
+  </si>
+  <si>
+    <t>공통영어2</t>
+  </si>
+  <si>
+    <t>24년</t>
+  </si>
+  <si>
+    <t>3월</t>
+  </si>
+  <si>
+    <t>6월</t>
+  </si>
+  <si>
+    <t>9월</t>
+  </si>
+  <si>
+    <t>고3</t>
+  </si>
+  <si>
+    <t>대수능</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -627,6 +766,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -651,8 +798,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -992,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -1003,10 +1151,11 @@
     <col min="6" max="10" width="20.85546875" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" customWidth="1"/>
     <col min="12" max="12" width="50.85546875" customWidth="1"/>
-    <col min="13" max="14" width="10.85546875" customWidth="1"/>
+    <col min="13" max="15" width="10.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1049,8 +1198,23 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P1" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>199</v>
+      </c>
+      <c r="R1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1076,7 +1240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -1114,7 +1278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1155,7 +1319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -1193,7 +1357,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -1234,7 +1398,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1260,7 +1424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -1286,7 +1450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -1324,7 +1488,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -1365,7 +1529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -1403,7 +1567,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>121</v>
       </c>
@@ -1441,7 +1605,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -1479,7 +1643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -1520,7 +1684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -1558,7 +1722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>111</v>
       </c>
@@ -1852,4 +2016,748 @@
     <ignoredError sqref="A1:B11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B405EBB-F6D6-3D4E-9DF9-DE7896AA98C4}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <cols>
+    <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" t="s">
+        <v>213</v>
+      </c>
+      <c r="D15" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" t="s">
+        <v>233</v>
+      </c>
+      <c r="C17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" t="s">
+        <v>227</v>
+      </c>
+      <c r="D23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C24" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B26" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>236</v>
+      </c>
+      <c r="E27" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>237</v>
+      </c>
+      <c r="E32" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" t="s">
+        <v>211</v>
+      </c>
+      <c r="D35" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" t="s">
+        <v>211</v>
+      </c>
+      <c r="D36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" t="s">
+        <v>234</v>
+      </c>
+      <c r="C37" t="s">
+        <v>211</v>
+      </c>
+      <c r="D37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" t="s">
+        <v>211</v>
+      </c>
+      <c r="D38" t="s">
+        <v>235</v>
+      </c>
+      <c r="E38" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" t="s">
+        <v>236</v>
+      </c>
+      <c r="E39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" t="s">
+        <v>211</v>
+      </c>
+      <c r="D41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42" t="s">
+        <v>238</v>
+      </c>
+      <c r="D42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E42" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" t="s">
+        <v>238</v>
+      </c>
+      <c r="D43" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" t="s">
+        <v>238</v>
+      </c>
+      <c r="D44" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" t="s">
+        <v>210</v>
+      </c>
+      <c r="C45" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E46" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>